--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487975_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487975_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.378</v>
+        <v>9.8978</v>
       </c>
       <c r="E2" t="n">
-        <v>8.2972</v>
+        <v>8.704700000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0808</v>
+        <v>1.1931</v>
       </c>
       <c r="G2" t="n">
         <v>7.1259</v>
@@ -610,13 +610,13 @@
         <v>2.1805</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.0852</v>
+        <v>-0.5654</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-0.5285</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1492</v>
+        <v>-0.0369</v>
       </c>
       <c r="V2" t="n">
         <v>1.1568</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.6573</v>
+        <v>5.7435</v>
       </c>
       <c r="E3" t="n">
-        <v>6.979</v>
+        <v>6.4302</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3216</v>
+        <v>-0.6867</v>
       </c>
       <c r="G3" t="n">
         <v>7.6447</v>
@@ -688,13 +688,13 @@
         <v>1.5858</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9532</v>
+        <v>0.0394</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5471</v>
+        <v>-0.0017</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4061</v>
+        <v>0.0411</v>
       </c>
       <c r="V3" t="n">
         <v>-1.5441</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.1105</v>
+        <v>4.9244</v>
       </c>
       <c r="E4" t="n">
-        <v>3.5644</v>
+        <v>3.4626</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5461</v>
+        <v>1.4619</v>
       </c>
       <c r="G4" t="n">
         <v>5.938</v>
@@ -766,13 +766,13 @@
         <v>1.3876</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8284</v>
+        <v>0.6423</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0552</v>
+        <v>-0.0467</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7733</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="V4" t="n">
         <v>-1.0612</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.0968</v>
+        <v>4.4691</v>
       </c>
       <c r="E5" t="n">
-        <v>3.0776</v>
+        <v>3.2814</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0192</v>
+        <v>1.1877</v>
       </c>
       <c r="G5" t="n">
         <v>3.3196</v>
@@ -844,13 +844,13 @@
         <v>0.7929</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.765</v>
+        <v>-0.3928</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8112</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0461</v>
+        <v>0.2146</v>
       </c>
       <c r="V5" t="n">
         <v>0.7494</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.1435</v>
+        <v>3.8452</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6481</v>
+        <v>1.3217</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4954</v>
+        <v>2.5235</v>
       </c>
       <c r="G6" t="n">
         <v>2.234</v>
@@ -922,13 +922,13 @@
         <v>2.5769</v>
       </c>
       <c r="S6" t="n">
-        <v>0.048</v>
+        <v>0.7497</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.624</v>
+        <v>0.0496</v>
       </c>
       <c r="U6" t="n">
-        <v>0.672</v>
+        <v>0.7000999999999999</v>
       </c>
       <c r="V6" t="n">
         <v>-0.7243000000000001</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.6223</v>
+        <v>2.8646</v>
       </c>
       <c r="E7" t="n">
-        <v>4.2425</v>
+        <v>4.3444</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.6202</v>
+        <v>-1.4798</v>
       </c>
       <c r="G7" t="n">
         <v>2.735</v>
@@ -1000,13 +1000,13 @@
         <v>0.7929</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2426</v>
+        <v>-1.0003</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8736</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.369</v>
+        <v>-0.2286</v>
       </c>
       <c r="V7" t="n">
         <v>0.337</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.9629</v>
+        <v>1.2883</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7259</v>
+        <v>-0.0891</v>
       </c>
       <c r="F8" t="n">
-        <v>1.237</v>
+        <v>1.3774</v>
       </c>
       <c r="G8" t="n">
         <v>0.0183</v>
@@ -1078,13 +1078,13 @@
         <v>0.7929</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2023</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>1.1087</v>
+        <v>0.2937</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0936</v>
+        <v>0.234</v>
       </c>
       <c r="V8" t="n">
         <v>0.9405</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5018</v>
+        <v>0.5504</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6262</v>
+        <v>-1.1563</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1279</v>
+        <v>1.7068</v>
       </c>
       <c r="G10" t="n">
         <v>-0.1354</v>
@@ -1234,13 +1234,13 @@
         <v>1.784</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.035</v>
+        <v>0.0137</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-0.4661</v>
       </c>
       <c r="U10" t="n">
-        <v>0.901</v>
+        <v>0.4798</v>
       </c>
       <c r="V10" t="n">
         <v>-0.1207</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.7628</v>
+        <v>-0.9675</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0915</v>
+        <v>-0.4366</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6713</v>
+        <v>-0.5309</v>
       </c>
       <c r="G11" t="n">
         <v>2.057</v>
@@ -1312,13 +1312,13 @@
         <v>1.3876</v>
       </c>
       <c r="S11" t="n">
-        <v>1.1802</v>
+        <v>0.9755</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9839</v>
+        <v>0.6388</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1963</v>
+        <v>0.3367</v>
       </c>
       <c r="V11" t="n">
         <v>-2.4142</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.9169</v>
+        <v>-1.8608</v>
       </c>
       <c r="E12" t="n">
         <v>-1.01</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9069</v>
+        <v>-0.8507</v>
       </c>
       <c r="G12" t="n">
         <v>-1.3025</v>
@@ -1390,13 +1390,13 @@
         <v>0.5947</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5352</v>
+        <v>-0.479</v>
       </c>
       <c r="T12" t="n">
         <v>-0.4368</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0984</v>
+        <v>-0.0422</v>
       </c>
       <c r="V12" t="n">
         <v>-0.674</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.6005</v>
+        <v>-2.5443</v>
       </c>
       <c r="E13" t="n">
         <v>-0.2918</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.3087</v>
+        <v>-2.2525</v>
       </c>
       <c r="G13" t="n">
         <v>-1.1812</v>
@@ -1468,13 +1468,13 @@
         <v>0.1982</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4104</v>
+        <v>-0.3542</v>
       </c>
       <c r="T13" t="n">
         <v>-0.312</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0984</v>
+        <v>-0.0422</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2071</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.9441</v>
+        <v>-2.6499</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.8132</v>
+        <v>-1.5471</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.1309</v>
+        <v>-1.1029</v>
       </c>
       <c r="G14" t="n">
         <v>-3.1208</v>
@@ -1546,13 +1546,13 @@
         <v>0.7929</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6163</v>
+        <v>-0.3221</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4992</v>
+        <v>-0.233</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1171</v>
+        <v>-0.089</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>25.85150000000001</v>
+        <v>26.1635</v>
       </c>
       <c r="E15" t="n">
-        <v>23.3047</v>
+        <v>23.6168</v>
       </c>
       <c r="F15" t="n">
-        <v>2.5468</v>
+        <v>2.5469</v>
       </c>
       <c r="G15" t="n">
         <v>25.9353</v>
@@ -1624,13 +1624,13 @@
         <v>14.8669</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4775999999999999</v>
+        <v>-0.1655</v>
       </c>
       <c r="T15" t="n">
-        <v>-2.7339</v>
+        <v>-2.4218</v>
       </c>
       <c r="U15" t="n">
-        <v>2.2563</v>
+        <v>2.2564</v>
       </c>
       <c r="V15" t="n">
         <v>-4.5619</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>V. PALOMO GIL</t>
+          <t>J. PAEZ AVILA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.939</v>
+        <v>2.7202</v>
       </c>
       <c r="E16" t="n">
-        <v>4.3138</v>
+        <v>1.7012</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.3748</v>
+        <v>1.019</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.9283</v>
+        <v>-0.5077</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.6349</v>
+        <v>-1.317</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.2935</v>
+        <v>0.8093</v>
       </c>
       <c r="J16" t="n">
-        <v>1.8695</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>1.7087</v>
+        <v>-0.5177</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1607</v>
+        <v>1.3298</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.7978</v>
+        <v>-1.3198</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.3436</v>
+        <v>-0.7993</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.4542</v>
+        <v>-0.5205</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5858</v>
+        <v>1.3876</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5858</v>
+        <v>1.3876</v>
       </c>
       <c r="S16" t="n">
-        <v>1.7374</v>
+        <v>-0.6442</v>
       </c>
       <c r="T16" t="n">
-        <v>1.2373</v>
+        <v>-0.5845</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5002</v>
+        <v>-0.0597</v>
       </c>
       <c r="V16" t="n">
-        <v>1.5441</v>
+        <v>2.4846</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2071</v>
+        <v>1.4737</v>
       </c>
       <c r="X16" t="n">
-        <v>0.337</v>
+        <v>1.0109</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. PAEZ AVILA</t>
+          <t>V. PALOMO GIL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.3657</v>
+        <v>1.9275</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5994</v>
+        <v>3.4989</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7663</v>
+        <v>-1.5714</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5077</v>
+        <v>-1.9283</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.317</v>
+        <v>-0.6349</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8093</v>
+        <v>-1.2935</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8120000000000001</v>
+        <v>1.8695</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.5177</v>
+        <v>1.7087</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3298</v>
+        <v>0.1607</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.3198</v>
+        <v>-3.7978</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7993</v>
+        <v>-2.3436</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5205</v>
+        <v>-1.4542</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3876</v>
+        <v>1.5858</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3876</v>
+        <v>1.5858</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9988</v>
+        <v>0.7259</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6864</v>
+        <v>0.4223</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3124</v>
+        <v>0.3036</v>
       </c>
       <c r="V17" t="n">
-        <v>2.4846</v>
+        <v>1.5441</v>
       </c>
       <c r="W17" t="n">
-        <v>1.4737</v>
+        <v>1.2071</v>
       </c>
       <c r="X17" t="n">
-        <v>1.0109</v>
+        <v>0.337</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. MARTIN GARCIA</t>
+          <t>J. PÁEZ ÁVILA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1529</v>
+        <v>0.6027</v>
       </c>
       <c r="E18" t="n">
-        <v>2.2163</v>
+        <v>0.6027</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0634</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0269</v>
+        <v>0.6027</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.281</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3079</v>
+        <v>0.6027</v>
       </c>
       <c r="J18" t="n">
-        <v>2.2932</v>
+        <v>0.6027</v>
       </c>
       <c r="K18" t="n">
-        <v>2.1325</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1607</v>
+        <v>0.6027</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.2662</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.4135</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1472</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3964</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.5947</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.5224</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9142</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6081</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. PÁEZ ÁVILA</t>
+          <t>J. MARTIN GARCIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6027</v>
+        <v>-0.0519</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6027</v>
+        <v>1.0957</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>-1.1477</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6027</v>
+        <v>0.0269</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>-0.281</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6027</v>
+        <v>0.3079</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6027</v>
+        <v>2.2932</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>2.1325</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6027</v>
+        <v>0.1607</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>-2.2662</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>-2.4135</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>0.1472</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>0.5947</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>0.3176</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>-0.2063</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>0.5239</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.587</v>
+        <v>-0.6327</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2502</v>
+        <v>1.1483</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.8372</v>
+        <v>-1.781</v>
       </c>
       <c r="G20" t="n">
         <v>-2.0429</v>
@@ -2014,13 +2014,13 @@
         <v>1.784</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0595</v>
+        <v>0.0138</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.121</v>
+        <v>-0.2229</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1805</v>
+        <v>0.2367</v>
       </c>
       <c r="V20" t="n">
         <v>0.6036</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8438</v>
+        <v>-0.9522</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2705</v>
+        <v>1.7798</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.1143</v>
+        <v>-2.7321</v>
       </c>
       <c r="G21" t="n">
         <v>-1.003</v>
@@ -2092,13 +2092,13 @@
         <v>0.7929</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9609</v>
+        <v>0.8525</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6753</v>
+        <v>-0.166</v>
       </c>
       <c r="U21" t="n">
-        <v>1.6363</v>
+        <v>1.0185</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6036</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.168</v>
+        <v>-2.6096</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1751</v>
+        <v>0.1305</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.9929</v>
+        <v>-2.7402</v>
       </c>
       <c r="G22" t="n">
         <v>-2.1891</v>
@@ -2170,13 +2170,13 @@
         <v>0.9911</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.5824</v>
+        <v>-1.0241</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9984</v>
+        <v>-0.6927</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5841</v>
+        <v>-0.3314</v>
       </c>
       <c r="V22" t="n">
         <v>0.6036</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.5184</v>
+        <v>-4.3636</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.6344</v>
+        <v>-2.227</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.8839</v>
+        <v>-2.1366</v>
       </c>
       <c r="G23" t="n">
         <v>-2.4475</v>
@@ -2248,13 +2248,13 @@
         <v>1.5858</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7338</v>
+        <v>-0.5790999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0608</v>
+        <v>-0.6533</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3269</v>
+        <v>0.0742</v>
       </c>
       <c r="V23" t="n">
         <v>-0.9405</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.9245</v>
+        <v>-5.8684</v>
       </c>
       <c r="E24" t="n">
         <v>-2.7744</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.1502</v>
+        <v>-3.094</v>
       </c>
       <c r="G24" t="n">
         <v>-4.2565</v>
@@ -2326,13 +2326,13 @@
         <v>0.1982</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3825</v>
+        <v>0.4387</v>
       </c>
       <c r="T24" t="n">
         <v>0.1286</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2539</v>
+        <v>0.3101</v>
       </c>
       <c r="V24" t="n">
         <v>-0.2666</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.2962</v>
+        <v>-6.4499</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.5634</v>
+        <v>-2.0541</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.7328</v>
+        <v>-4.3959</v>
       </c>
       <c r="G25" t="n">
         <v>-4.7097</v>
@@ -2404,13 +2404,13 @@
         <v>0.3964</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7848000000000001</v>
+        <v>0.0615</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8736</v>
+        <v>-0.3642</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0888</v>
+        <v>0.4257</v>
       </c>
       <c r="V25" t="n">
         <v>-1.2071</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-10.5739</v>
+        <v>-10.1736</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.6524</v>
+        <v>-5.4486</v>
       </c>
       <c r="F26" t="n">
-        <v>-4.9215</v>
+        <v>-4.725</v>
       </c>
       <c r="G26" t="n">
         <v>-7.4802</v>
@@ -2482,13 +2482,13 @@
         <v>0.5947</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.08550000000000001</v>
+        <v>0.3148</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.121</v>
+        <v>0.0827</v>
       </c>
       <c r="U26" t="n">
-        <v>0.0355</v>
+        <v>0.2321</v>
       </c>
       <c r="V26" t="n">
         <v>2.3438</v>
@@ -2518,10 +2518,10 @@
         <v>-25.8515</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.546800000000002</v>
+        <v>-2.547</v>
       </c>
       <c r="F27" t="n">
-        <v>-23.3047</v>
+        <v>-23.3049</v>
       </c>
       <c r="G27" t="n">
         <v>-25.9353</v>
@@ -2560,10 +2560,10 @@
         <v>9.911199999999999</v>
       </c>
       <c r="S27" t="n">
-        <v>0.4773999999999998</v>
+        <v>0.4774000000000001</v>
       </c>
       <c r="T27" t="n">
-        <v>-2.2564</v>
+        <v>-2.2563</v>
       </c>
       <c r="U27" t="n">
         <v>2.7337</v>
